--- a/employee_surveys/045_employee_competency_mapping_evaluation_form--employee_surveys.xlsx
+++ b/employee_surveys/045_employee_competency_mapping_evaluation_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leadership',_'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leadership', 'value': 'leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'communication',_'value':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Communication', 'value': 'communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'time_management',_'value':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Time Management', 'value': 'time_management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'problem-solving',_'value':_'problem_solving'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Problem-solving', 'value': 'problem_solving'}</t>
+          <t>Problem-solving</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'adaptability',_'value':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Adaptability', 'value': 'adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'team_management',_'value':_'team_management'}</t>
+          <t>team_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Team Management', 'value': 'team_management'}</t>
+          <t>Team Management</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'interpersonal_skills',_'value':_'interpersonal_skills'}</t>
+          <t>interpersonal_skills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Interpersonal Skills', 'value': 'interpersonal_skills'}</t>
+          <t>Interpersonal Skills</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'results-driven',_'value':_'results_driven'}</t>
+          <t>results-driven</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Results-driven', 'value': 'results_driven'}</t>
+          <t>Results-driven</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'continuous_learning',_'value':_'continuous_learning'}</t>
+          <t>continuous_learning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Continuous Learning', 'value': 'continuous_learning'}</t>
+          <t>Continuous Learning</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'strategic_thinking',_'value':_'strategic_thinking'}</t>
+          <t>strategic_thinking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Strategic Thinking', 'value': 'strategic_thinking'}</t>
+          <t>Strategic Thinking</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'collaboration',_'value':_'collaboration'}</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Collaboration', 'value': 'collaboration'}</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'innovation',_'value':_'innovation'}</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Innovation', 'value': 'innovation'}</t>
+          <t>Innovation</t>
         </is>
       </c>
     </row>
